--- a/output/pdf_financials_xlsx/EGR.xlsx
+++ b/output/pdf_financials_xlsx/EGR.xlsx
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.900793</v>
+        <v>-0.900848</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.515629</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.900295</v>
+        <v>-0.90035</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.515267</v>
@@ -1978,37 +1978,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.012658</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017449</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00232</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.781788</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.303363</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.056286</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.069472</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.199582</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.157461</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.245647</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.035174</v>
       </c>
     </row>
     <row r="35">
@@ -2058,37 +2058,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.012658</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017449</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00232</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.781788</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.303363</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.056286</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.069472</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.199582</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.157461</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.245647</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.045</v>
+        <v>0.080174</v>
       </c>
     </row>
     <row r="37">
@@ -2538,37 +2538,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.012658</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.017449</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004485</v>
+        <v>0.002165</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.865179</v>
+        <v>0.08339100000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.322184</v>
+        <v>0.018821</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.095974</v>
+        <v>0.039688</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.126685</v>
+        <v>0.057213</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.215068</v>
+        <v>0.015486</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.187035</v>
+        <v>0.029574</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.263916</v>
+        <v>0.018269</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.043632</v>
+        <v>0.008458</v>
       </c>
     </row>
     <row r="49">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
@@ -35393,7 +35393,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E418" s="5" t="n">

--- a/output/pdf_financials_xlsx/EGR.xlsx
+++ b/output/pdf_financials_xlsx/EGR.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.087827</v>
+        <v>0.177827</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.058839</v>
+        <v>0.148839</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.06854</v>
+        <v>0.15854</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.159269</v>
+        <v>0.179969</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.376301</v>
+        <v>0.418301</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.163588</v>
+        <v>0.184588</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.182145</v>
+        <v>0.238645</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -5083,13 +5083,13 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.032238</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.024762</v>
       </c>
     </row>
     <row r="111">
@@ -19663,7 +19663,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -20777,7 +20781,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -24046,7 +24054,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -26318,7 +26330,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E289" s="5" t="n">
         <v>0.282306</v>
       </c>
@@ -27525,7 +27541,11 @@
           <t>Management and director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -31311,7 +31331,11 @@
           <t>Management and director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -32792,7 +32816,11 @@
           <t>Management and director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -34271,7 +34299,11 @@
           <t>Management and director fees 10</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E402" s="5" t="n">
         <v>0.09</v>
       </c>
